--- a/templates/quote_template.xlsx
+++ b/templates/quote_template.xlsx
@@ -1286,7 +1286,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1433,6 +1433,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="90">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -2073,214 +2079,214 @@
         <v/>
       </c>
       <c r="I8" s="47" t="n"/>
-      <c r="J8" s="20" t="n"/>
-      <c r="K8" s="21" t="n"/>
-      <c r="L8" s="21" t="n"/>
-      <c r="M8" s="21" t="n"/>
-      <c r="N8" s="21" t="n"/>
-      <c r="O8" s="21" t="n"/>
-      <c r="P8" s="21" t="n"/>
-      <c r="Q8" s="21" t="n"/>
-      <c r="R8" s="21" t="n"/>
-      <c r="S8" s="21" t="n"/>
-      <c r="T8" s="21" t="n"/>
-      <c r="U8" s="21" t="n"/>
-      <c r="V8" s="21" t="n"/>
-      <c r="W8" s="21" t="n"/>
-      <c r="X8" s="21" t="n"/>
-      <c r="Y8" s="21" t="n"/>
-      <c r="Z8" s="21" t="n"/>
-      <c r="AA8" s="21" t="n"/>
-      <c r="AB8" s="21" t="n"/>
-      <c r="AC8" s="21" t="n"/>
-      <c r="AD8" s="21" t="n"/>
-      <c r="AE8" s="21" t="n"/>
-      <c r="AF8" s="21" t="n"/>
-      <c r="AG8" s="21" t="n"/>
-      <c r="AH8" s="21" t="n"/>
-      <c r="AI8" s="21" t="n"/>
-      <c r="AJ8" s="21" t="n"/>
-      <c r="AK8" s="21" t="n"/>
-      <c r="AL8" s="21" t="n"/>
-      <c r="AM8" s="21" t="n"/>
-      <c r="AN8" s="21" t="n"/>
-      <c r="AO8" s="21" t="n"/>
-      <c r="AP8" s="21" t="n"/>
-      <c r="AQ8" s="21" t="n"/>
-      <c r="AR8" s="21" t="n"/>
-      <c r="AS8" s="21" t="n"/>
-      <c r="AT8" s="21" t="n"/>
-      <c r="AU8" s="21" t="n"/>
-      <c r="AV8" s="21" t="n"/>
-      <c r="AW8" s="21" t="n"/>
-      <c r="AX8" s="21" t="n"/>
-      <c r="AY8" s="21" t="n"/>
-      <c r="AZ8" s="21" t="n"/>
-      <c r="BA8" s="21" t="n"/>
-      <c r="BB8" s="21" t="n"/>
-      <c r="BC8" s="21" t="n"/>
-      <c r="BD8" s="21" t="n"/>
-      <c r="BE8" s="21" t="n"/>
-      <c r="BF8" s="21" t="n"/>
-      <c r="BG8" s="21" t="n"/>
-      <c r="BH8" s="21" t="n"/>
-      <c r="BI8" s="21" t="n"/>
-      <c r="BJ8" s="21" t="n"/>
-      <c r="BK8" s="21" t="n"/>
-      <c r="BL8" s="21" t="n"/>
-      <c r="BM8" s="21" t="n"/>
-      <c r="BN8" s="21" t="n"/>
-      <c r="BO8" s="21" t="n"/>
-      <c r="BP8" s="21" t="n"/>
-      <c r="BQ8" s="21" t="n"/>
-      <c r="BR8" s="21" t="n"/>
-      <c r="BS8" s="21" t="n"/>
-      <c r="BT8" s="21" t="n"/>
-      <c r="BU8" s="21" t="n"/>
-      <c r="BV8" s="21" t="n"/>
-      <c r="BW8" s="21" t="n"/>
-      <c r="BX8" s="21" t="n"/>
-      <c r="BY8" s="21" t="n"/>
-      <c r="BZ8" s="21" t="n"/>
-      <c r="CA8" s="21" t="n"/>
-      <c r="CB8" s="21" t="n"/>
-      <c r="CC8" s="21" t="n"/>
-      <c r="CD8" s="21" t="n"/>
-      <c r="CE8" s="21" t="n"/>
-      <c r="CF8" s="21" t="n"/>
-      <c r="CG8" s="21" t="n"/>
-      <c r="CH8" s="21" t="n"/>
-      <c r="CI8" s="21" t="n"/>
-      <c r="CJ8" s="21" t="n"/>
-      <c r="CK8" s="21" t="n"/>
-      <c r="CL8" s="21" t="n"/>
-      <c r="CM8" s="21" t="n"/>
-      <c r="CN8" s="21" t="n"/>
-      <c r="CO8" s="21" t="n"/>
-      <c r="CP8" s="21" t="n"/>
-      <c r="CQ8" s="21" t="n"/>
-      <c r="CR8" s="21" t="n"/>
-      <c r="CS8" s="21" t="n"/>
-      <c r="CT8" s="21" t="n"/>
-      <c r="CU8" s="21" t="n"/>
-      <c r="CV8" s="21" t="n"/>
-      <c r="CW8" s="21" t="n"/>
-      <c r="CX8" s="21" t="n"/>
-      <c r="CY8" s="21" t="n"/>
-      <c r="CZ8" s="21" t="n"/>
-      <c r="DA8" s="21" t="n"/>
-      <c r="DB8" s="21" t="n"/>
-      <c r="DC8" s="21" t="n"/>
-      <c r="DD8" s="21" t="n"/>
-      <c r="DE8" s="21" t="n"/>
-      <c r="DF8" s="21" t="n"/>
-      <c r="DG8" s="21" t="n"/>
-      <c r="DH8" s="21" t="n"/>
-      <c r="DI8" s="21" t="n"/>
-      <c r="DJ8" s="21" t="n"/>
-      <c r="DK8" s="21" t="n"/>
-      <c r="DL8" s="21" t="n"/>
-      <c r="DM8" s="21" t="n"/>
-      <c r="DN8" s="21" t="n"/>
-      <c r="DO8" s="21" t="n"/>
-      <c r="DP8" s="21" t="n"/>
-      <c r="DQ8" s="21" t="n"/>
-      <c r="DR8" s="21" t="n"/>
-      <c r="DS8" s="21" t="n"/>
-      <c r="DT8" s="21" t="n"/>
-      <c r="DU8" s="21" t="n"/>
-      <c r="DV8" s="21" t="n"/>
-      <c r="DW8" s="21" t="n"/>
-      <c r="DX8" s="21" t="n"/>
-      <c r="DY8" s="21" t="n"/>
-      <c r="DZ8" s="21" t="n"/>
-      <c r="EA8" s="21" t="n"/>
-      <c r="EB8" s="21" t="n"/>
-      <c r="EC8" s="21" t="n"/>
-      <c r="ED8" s="21" t="n"/>
-      <c r="EE8" s="21" t="n"/>
-      <c r="EF8" s="21" t="n"/>
-      <c r="EG8" s="21" t="n"/>
-      <c r="EH8" s="21" t="n"/>
-      <c r="EI8" s="21" t="n"/>
-      <c r="EJ8" s="21" t="n"/>
-      <c r="EK8" s="21" t="n"/>
-      <c r="EL8" s="21" t="n"/>
-      <c r="EM8" s="21" t="n"/>
-      <c r="EN8" s="21" t="n"/>
-      <c r="EO8" s="21" t="n"/>
-      <c r="EP8" s="21" t="n"/>
-      <c r="EQ8" s="21" t="n"/>
-      <c r="ER8" s="21" t="n"/>
-      <c r="ES8" s="21" t="n"/>
-      <c r="ET8" s="21" t="n"/>
-      <c r="EU8" s="21" t="n"/>
-      <c r="EV8" s="21" t="n"/>
-      <c r="EW8" s="21" t="n"/>
-      <c r="EX8" s="21" t="n"/>
-      <c r="EY8" s="21" t="n"/>
-      <c r="EZ8" s="21" t="n"/>
-      <c r="FA8" s="21" t="n"/>
-      <c r="FB8" s="21" t="n"/>
-      <c r="FC8" s="21" t="n"/>
-      <c r="FD8" s="21" t="n"/>
-      <c r="FE8" s="21" t="n"/>
-      <c r="FF8" s="21" t="n"/>
-      <c r="FG8" s="21" t="n"/>
-      <c r="FH8" s="21" t="n"/>
-      <c r="FI8" s="21" t="n"/>
-      <c r="FJ8" s="21" t="n"/>
-      <c r="FK8" s="21" t="n"/>
-      <c r="FL8" s="21" t="n"/>
-      <c r="FM8" s="21" t="n"/>
-      <c r="FN8" s="21" t="n"/>
-      <c r="FO8" s="21" t="n"/>
-      <c r="FP8" s="21" t="n"/>
-      <c r="FQ8" s="21" t="n"/>
-      <c r="FR8" s="21" t="n"/>
-      <c r="FS8" s="21" t="n"/>
-      <c r="FT8" s="21" t="n"/>
-      <c r="FU8" s="21" t="n"/>
-      <c r="FV8" s="21" t="n"/>
-      <c r="FW8" s="21" t="n"/>
-      <c r="FX8" s="21" t="n"/>
-      <c r="FY8" s="21" t="n"/>
-      <c r="FZ8" s="21" t="n"/>
-      <c r="GA8" s="21" t="n"/>
-      <c r="GB8" s="21" t="n"/>
-      <c r="GC8" s="21" t="n"/>
-      <c r="GD8" s="21" t="n"/>
-      <c r="GE8" s="21" t="n"/>
-      <c r="GF8" s="21" t="n"/>
-      <c r="GG8" s="21" t="n"/>
-      <c r="GH8" s="21" t="n"/>
-      <c r="GI8" s="21" t="n"/>
-      <c r="GJ8" s="21" t="n"/>
-      <c r="GK8" s="21" t="n"/>
-      <c r="GL8" s="21" t="n"/>
-      <c r="GM8" s="21" t="n"/>
-      <c r="GN8" s="21" t="n"/>
-      <c r="GO8" s="21" t="n"/>
-      <c r="GP8" s="21" t="n"/>
-      <c r="GQ8" s="21" t="n"/>
-      <c r="GR8" s="21" t="n"/>
-      <c r="GS8" s="21" t="n"/>
-      <c r="GT8" s="21" t="n"/>
-      <c r="GU8" s="21" t="n"/>
-      <c r="GV8" s="21" t="n"/>
-      <c r="GW8" s="21" t="n"/>
-      <c r="GX8" s="21" t="n"/>
-      <c r="GY8" s="21" t="n"/>
-      <c r="GZ8" s="21" t="n"/>
-      <c r="HA8" s="21" t="n"/>
-      <c r="HB8" s="21" t="n"/>
-      <c r="HC8" s="21" t="n"/>
-      <c r="HD8" s="21" t="n"/>
-      <c r="HE8" s="21" t="n"/>
-      <c r="HF8" s="21" t="n"/>
-      <c r="HG8" s="21" t="n"/>
-      <c r="HH8" s="21" t="n"/>
-      <c r="HI8" s="21" t="n"/>
+      <c r="J8" s="60" t="n"/>
+      <c r="K8" s="39" t="n"/>
+      <c r="L8" s="39" t="n"/>
+      <c r="M8" s="39" t="n"/>
+      <c r="N8" s="39" t="n"/>
+      <c r="O8" s="39" t="n"/>
+      <c r="P8" s="39" t="n"/>
+      <c r="Q8" s="39" t="n"/>
+      <c r="R8" s="39" t="n"/>
+      <c r="S8" s="39" t="n"/>
+      <c r="T8" s="39" t="n"/>
+      <c r="U8" s="39" t="n"/>
+      <c r="V8" s="39" t="n"/>
+      <c r="W8" s="39" t="n"/>
+      <c r="X8" s="39" t="n"/>
+      <c r="Y8" s="39" t="n"/>
+      <c r="Z8" s="39" t="n"/>
+      <c r="AA8" s="39" t="n"/>
+      <c r="AB8" s="39" t="n"/>
+      <c r="AC8" s="39" t="n"/>
+      <c r="AD8" s="39" t="n"/>
+      <c r="AE8" s="39" t="n"/>
+      <c r="AF8" s="39" t="n"/>
+      <c r="AG8" s="39" t="n"/>
+      <c r="AH8" s="39" t="n"/>
+      <c r="AI8" s="39" t="n"/>
+      <c r="AJ8" s="39" t="n"/>
+      <c r="AK8" s="39" t="n"/>
+      <c r="AL8" s="39" t="n"/>
+      <c r="AM8" s="39" t="n"/>
+      <c r="AN8" s="39" t="n"/>
+      <c r="AO8" s="39" t="n"/>
+      <c r="AP8" s="39" t="n"/>
+      <c r="AQ8" s="39" t="n"/>
+      <c r="AR8" s="39" t="n"/>
+      <c r="AS8" s="39" t="n"/>
+      <c r="AT8" s="39" t="n"/>
+      <c r="AU8" s="39" t="n"/>
+      <c r="AV8" s="39" t="n"/>
+      <c r="AW8" s="39" t="n"/>
+      <c r="AX8" s="39" t="n"/>
+      <c r="AY8" s="39" t="n"/>
+      <c r="AZ8" s="39" t="n"/>
+      <c r="BA8" s="39" t="n"/>
+      <c r="BB8" s="39" t="n"/>
+      <c r="BC8" s="39" t="n"/>
+      <c r="BD8" s="39" t="n"/>
+      <c r="BE8" s="39" t="n"/>
+      <c r="BF8" s="39" t="n"/>
+      <c r="BG8" s="39" t="n"/>
+      <c r="BH8" s="39" t="n"/>
+      <c r="BI8" s="39" t="n"/>
+      <c r="BJ8" s="39" t="n"/>
+      <c r="BK8" s="39" t="n"/>
+      <c r="BL8" s="39" t="n"/>
+      <c r="BM8" s="39" t="n"/>
+      <c r="BN8" s="39" t="n"/>
+      <c r="BO8" s="39" t="n"/>
+      <c r="BP8" s="39" t="n"/>
+      <c r="BQ8" s="39" t="n"/>
+      <c r="BR8" s="39" t="n"/>
+      <c r="BS8" s="39" t="n"/>
+      <c r="BT8" s="39" t="n"/>
+      <c r="BU8" s="39" t="n"/>
+      <c r="BV8" s="39" t="n"/>
+      <c r="BW8" s="39" t="n"/>
+      <c r="BX8" s="39" t="n"/>
+      <c r="BY8" s="39" t="n"/>
+      <c r="BZ8" s="39" t="n"/>
+      <c r="CA8" s="39" t="n"/>
+      <c r="CB8" s="39" t="n"/>
+      <c r="CC8" s="39" t="n"/>
+      <c r="CD8" s="39" t="n"/>
+      <c r="CE8" s="39" t="n"/>
+      <c r="CF8" s="39" t="n"/>
+      <c r="CG8" s="39" t="n"/>
+      <c r="CH8" s="39" t="n"/>
+      <c r="CI8" s="39" t="n"/>
+      <c r="CJ8" s="39" t="n"/>
+      <c r="CK8" s="39" t="n"/>
+      <c r="CL8" s="39" t="n"/>
+      <c r="CM8" s="39" t="n"/>
+      <c r="CN8" s="39" t="n"/>
+      <c r="CO8" s="39" t="n"/>
+      <c r="CP8" s="39" t="n"/>
+      <c r="CQ8" s="39" t="n"/>
+      <c r="CR8" s="39" t="n"/>
+      <c r="CS8" s="39" t="n"/>
+      <c r="CT8" s="39" t="n"/>
+      <c r="CU8" s="39" t="n"/>
+      <c r="CV8" s="39" t="n"/>
+      <c r="CW8" s="39" t="n"/>
+      <c r="CX8" s="39" t="n"/>
+      <c r="CY8" s="39" t="n"/>
+      <c r="CZ8" s="39" t="n"/>
+      <c r="DA8" s="39" t="n"/>
+      <c r="DB8" s="39" t="n"/>
+      <c r="DC8" s="39" t="n"/>
+      <c r="DD8" s="39" t="n"/>
+      <c r="DE8" s="39" t="n"/>
+      <c r="DF8" s="39" t="n"/>
+      <c r="DG8" s="39" t="n"/>
+      <c r="DH8" s="39" t="n"/>
+      <c r="DI8" s="39" t="n"/>
+      <c r="DJ8" s="39" t="n"/>
+      <c r="DK8" s="39" t="n"/>
+      <c r="DL8" s="39" t="n"/>
+      <c r="DM8" s="39" t="n"/>
+      <c r="DN8" s="39" t="n"/>
+      <c r="DO8" s="39" t="n"/>
+      <c r="DP8" s="39" t="n"/>
+      <c r="DQ8" s="39" t="n"/>
+      <c r="DR8" s="39" t="n"/>
+      <c r="DS8" s="39" t="n"/>
+      <c r="DT8" s="39" t="n"/>
+      <c r="DU8" s="39" t="n"/>
+      <c r="DV8" s="39" t="n"/>
+      <c r="DW8" s="39" t="n"/>
+      <c r="DX8" s="39" t="n"/>
+      <c r="DY8" s="39" t="n"/>
+      <c r="DZ8" s="39" t="n"/>
+      <c r="EA8" s="39" t="n"/>
+      <c r="EB8" s="39" t="n"/>
+      <c r="EC8" s="39" t="n"/>
+      <c r="ED8" s="39" t="n"/>
+      <c r="EE8" s="39" t="n"/>
+      <c r="EF8" s="39" t="n"/>
+      <c r="EG8" s="39" t="n"/>
+      <c r="EH8" s="39" t="n"/>
+      <c r="EI8" s="39" t="n"/>
+      <c r="EJ8" s="39" t="n"/>
+      <c r="EK8" s="39" t="n"/>
+      <c r="EL8" s="39" t="n"/>
+      <c r="EM8" s="39" t="n"/>
+      <c r="EN8" s="39" t="n"/>
+      <c r="EO8" s="39" t="n"/>
+      <c r="EP8" s="39" t="n"/>
+      <c r="EQ8" s="39" t="n"/>
+      <c r="ER8" s="39" t="n"/>
+      <c r="ES8" s="39" t="n"/>
+      <c r="ET8" s="39" t="n"/>
+      <c r="EU8" s="39" t="n"/>
+      <c r="EV8" s="39" t="n"/>
+      <c r="EW8" s="39" t="n"/>
+      <c r="EX8" s="39" t="n"/>
+      <c r="EY8" s="39" t="n"/>
+      <c r="EZ8" s="39" t="n"/>
+      <c r="FA8" s="39" t="n"/>
+      <c r="FB8" s="39" t="n"/>
+      <c r="FC8" s="39" t="n"/>
+      <c r="FD8" s="39" t="n"/>
+      <c r="FE8" s="39" t="n"/>
+      <c r="FF8" s="39" t="n"/>
+      <c r="FG8" s="39" t="n"/>
+      <c r="FH8" s="39" t="n"/>
+      <c r="FI8" s="39" t="n"/>
+      <c r="FJ8" s="39" t="n"/>
+      <c r="FK8" s="39" t="n"/>
+      <c r="FL8" s="39" t="n"/>
+      <c r="FM8" s="39" t="n"/>
+      <c r="FN8" s="39" t="n"/>
+      <c r="FO8" s="39" t="n"/>
+      <c r="FP8" s="39" t="n"/>
+      <c r="FQ8" s="39" t="n"/>
+      <c r="FR8" s="39" t="n"/>
+      <c r="FS8" s="39" t="n"/>
+      <c r="FT8" s="39" t="n"/>
+      <c r="FU8" s="39" t="n"/>
+      <c r="FV8" s="39" t="n"/>
+      <c r="FW8" s="39" t="n"/>
+      <c r="FX8" s="39" t="n"/>
+      <c r="FY8" s="39" t="n"/>
+      <c r="FZ8" s="39" t="n"/>
+      <c r="GA8" s="39" t="n"/>
+      <c r="GB8" s="39" t="n"/>
+      <c r="GC8" s="39" t="n"/>
+      <c r="GD8" s="39" t="n"/>
+      <c r="GE8" s="39" t="n"/>
+      <c r="GF8" s="39" t="n"/>
+      <c r="GG8" s="39" t="n"/>
+      <c r="GH8" s="39" t="n"/>
+      <c r="GI8" s="39" t="n"/>
+      <c r="GJ8" s="39" t="n"/>
+      <c r="GK8" s="39" t="n"/>
+      <c r="GL8" s="39" t="n"/>
+      <c r="GM8" s="39" t="n"/>
+      <c r="GN8" s="39" t="n"/>
+      <c r="GO8" s="39" t="n"/>
+      <c r="GP8" s="39" t="n"/>
+      <c r="GQ8" s="39" t="n"/>
+      <c r="GR8" s="39" t="n"/>
+      <c r="GS8" s="39" t="n"/>
+      <c r="GT8" s="39" t="n"/>
+      <c r="GU8" s="39" t="n"/>
+      <c r="GV8" s="39" t="n"/>
+      <c r="GW8" s="39" t="n"/>
+      <c r="GX8" s="39" t="n"/>
+      <c r="GY8" s="39" t="n"/>
+      <c r="GZ8" s="39" t="n"/>
+      <c r="HA8" s="39" t="n"/>
+      <c r="HB8" s="39" t="n"/>
+      <c r="HC8" s="39" t="n"/>
+      <c r="HD8" s="39" t="n"/>
+      <c r="HE8" s="39" t="n"/>
+      <c r="HF8" s="39" t="n"/>
+      <c r="HG8" s="39" t="n"/>
+      <c r="HH8" s="39" t="n"/>
+      <c r="HI8" s="39" t="n"/>
     </row>
     <row r="9" ht="44.1" customFormat="1" customHeight="1" s="1">
       <c r="A9" s="16" t="n">
@@ -2317,214 +2323,214 @@
         <v/>
       </c>
       <c r="I9" s="49" t="n"/>
-      <c r="J9" s="23" t="n"/>
-      <c r="K9" s="21" t="n"/>
-      <c r="L9" s="21" t="n"/>
-      <c r="M9" s="21" t="n"/>
-      <c r="N9" s="21" t="n"/>
-      <c r="O9" s="21" t="n"/>
-      <c r="P9" s="21" t="n"/>
-      <c r="Q9" s="21" t="n"/>
-      <c r="R9" s="21" t="n"/>
-      <c r="S9" s="21" t="n"/>
-      <c r="T9" s="21" t="n"/>
-      <c r="U9" s="21" t="n"/>
-      <c r="V9" s="21" t="n"/>
-      <c r="W9" s="21" t="n"/>
-      <c r="X9" s="21" t="n"/>
-      <c r="Y9" s="21" t="n"/>
-      <c r="Z9" s="21" t="n"/>
-      <c r="AA9" s="21" t="n"/>
-      <c r="AB9" s="21" t="n"/>
-      <c r="AC9" s="21" t="n"/>
-      <c r="AD9" s="21" t="n"/>
-      <c r="AE9" s="21" t="n"/>
-      <c r="AF9" s="21" t="n"/>
-      <c r="AG9" s="21" t="n"/>
-      <c r="AH9" s="21" t="n"/>
-      <c r="AI9" s="21" t="n"/>
-      <c r="AJ9" s="21" t="n"/>
-      <c r="AK9" s="21" t="n"/>
-      <c r="AL9" s="21" t="n"/>
-      <c r="AM9" s="21" t="n"/>
-      <c r="AN9" s="21" t="n"/>
-      <c r="AO9" s="21" t="n"/>
-      <c r="AP9" s="21" t="n"/>
-      <c r="AQ9" s="21" t="n"/>
-      <c r="AR9" s="21" t="n"/>
-      <c r="AS9" s="21" t="n"/>
-      <c r="AT9" s="21" t="n"/>
-      <c r="AU9" s="21" t="n"/>
-      <c r="AV9" s="21" t="n"/>
-      <c r="AW9" s="21" t="n"/>
-      <c r="AX9" s="21" t="n"/>
-      <c r="AY9" s="21" t="n"/>
-      <c r="AZ9" s="21" t="n"/>
-      <c r="BA9" s="21" t="n"/>
-      <c r="BB9" s="21" t="n"/>
-      <c r="BC9" s="21" t="n"/>
-      <c r="BD9" s="21" t="n"/>
-      <c r="BE9" s="21" t="n"/>
-      <c r="BF9" s="21" t="n"/>
-      <c r="BG9" s="21" t="n"/>
-      <c r="BH9" s="21" t="n"/>
-      <c r="BI9" s="21" t="n"/>
-      <c r="BJ9" s="21" t="n"/>
-      <c r="BK9" s="21" t="n"/>
-      <c r="BL9" s="21" t="n"/>
-      <c r="BM9" s="21" t="n"/>
-      <c r="BN9" s="21" t="n"/>
-      <c r="BO9" s="21" t="n"/>
-      <c r="BP9" s="21" t="n"/>
-      <c r="BQ9" s="21" t="n"/>
-      <c r="BR9" s="21" t="n"/>
-      <c r="BS9" s="21" t="n"/>
-      <c r="BT9" s="21" t="n"/>
-      <c r="BU9" s="21" t="n"/>
-      <c r="BV9" s="21" t="n"/>
-      <c r="BW9" s="21" t="n"/>
-      <c r="BX9" s="21" t="n"/>
-      <c r="BY9" s="21" t="n"/>
-      <c r="BZ9" s="21" t="n"/>
-      <c r="CA9" s="21" t="n"/>
-      <c r="CB9" s="21" t="n"/>
-      <c r="CC9" s="21" t="n"/>
-      <c r="CD9" s="21" t="n"/>
-      <c r="CE9" s="21" t="n"/>
-      <c r="CF9" s="21" t="n"/>
-      <c r="CG9" s="21" t="n"/>
-      <c r="CH9" s="21" t="n"/>
-      <c r="CI9" s="21" t="n"/>
-      <c r="CJ9" s="21" t="n"/>
-      <c r="CK9" s="21" t="n"/>
-      <c r="CL9" s="21" t="n"/>
-      <c r="CM9" s="21" t="n"/>
-      <c r="CN9" s="21" t="n"/>
-      <c r="CO9" s="21" t="n"/>
-      <c r="CP9" s="21" t="n"/>
-      <c r="CQ9" s="21" t="n"/>
-      <c r="CR9" s="21" t="n"/>
-      <c r="CS9" s="21" t="n"/>
-      <c r="CT9" s="21" t="n"/>
-      <c r="CU9" s="21" t="n"/>
-      <c r="CV9" s="21" t="n"/>
-      <c r="CW9" s="21" t="n"/>
-      <c r="CX9" s="21" t="n"/>
-      <c r="CY9" s="21" t="n"/>
-      <c r="CZ9" s="21" t="n"/>
-      <c r="DA9" s="21" t="n"/>
-      <c r="DB9" s="21" t="n"/>
-      <c r="DC9" s="21" t="n"/>
-      <c r="DD9" s="21" t="n"/>
-      <c r="DE9" s="21" t="n"/>
-      <c r="DF9" s="21" t="n"/>
-      <c r="DG9" s="21" t="n"/>
-      <c r="DH9" s="21" t="n"/>
-      <c r="DI9" s="21" t="n"/>
-      <c r="DJ9" s="21" t="n"/>
-      <c r="DK9" s="21" t="n"/>
-      <c r="DL9" s="21" t="n"/>
-      <c r="DM9" s="21" t="n"/>
-      <c r="DN9" s="21" t="n"/>
-      <c r="DO9" s="21" t="n"/>
-      <c r="DP9" s="21" t="n"/>
-      <c r="DQ9" s="21" t="n"/>
-      <c r="DR9" s="21" t="n"/>
-      <c r="DS9" s="21" t="n"/>
-      <c r="DT9" s="21" t="n"/>
-      <c r="DU9" s="21" t="n"/>
-      <c r="DV9" s="21" t="n"/>
-      <c r="DW9" s="21" t="n"/>
-      <c r="DX9" s="21" t="n"/>
-      <c r="DY9" s="21" t="n"/>
-      <c r="DZ9" s="21" t="n"/>
-      <c r="EA9" s="21" t="n"/>
-      <c r="EB9" s="21" t="n"/>
-      <c r="EC9" s="21" t="n"/>
-      <c r="ED9" s="21" t="n"/>
-      <c r="EE9" s="21" t="n"/>
-      <c r="EF9" s="21" t="n"/>
-      <c r="EG9" s="21" t="n"/>
-      <c r="EH9" s="21" t="n"/>
-      <c r="EI9" s="21" t="n"/>
-      <c r="EJ9" s="21" t="n"/>
-      <c r="EK9" s="21" t="n"/>
-      <c r="EL9" s="21" t="n"/>
-      <c r="EM9" s="21" t="n"/>
-      <c r="EN9" s="21" t="n"/>
-      <c r="EO9" s="21" t="n"/>
-      <c r="EP9" s="21" t="n"/>
-      <c r="EQ9" s="21" t="n"/>
-      <c r="ER9" s="21" t="n"/>
-      <c r="ES9" s="21" t="n"/>
-      <c r="ET9" s="21" t="n"/>
-      <c r="EU9" s="21" t="n"/>
-      <c r="EV9" s="21" t="n"/>
-      <c r="EW9" s="21" t="n"/>
-      <c r="EX9" s="21" t="n"/>
-      <c r="EY9" s="21" t="n"/>
-      <c r="EZ9" s="21" t="n"/>
-      <c r="FA9" s="21" t="n"/>
-      <c r="FB9" s="21" t="n"/>
-      <c r="FC9" s="21" t="n"/>
-      <c r="FD9" s="21" t="n"/>
-      <c r="FE9" s="21" t="n"/>
-      <c r="FF9" s="21" t="n"/>
-      <c r="FG9" s="21" t="n"/>
-      <c r="FH9" s="21" t="n"/>
-      <c r="FI9" s="21" t="n"/>
-      <c r="FJ9" s="21" t="n"/>
-      <c r="FK9" s="21" t="n"/>
-      <c r="FL9" s="21" t="n"/>
-      <c r="FM9" s="21" t="n"/>
-      <c r="FN9" s="21" t="n"/>
-      <c r="FO9" s="21" t="n"/>
-      <c r="FP9" s="21" t="n"/>
-      <c r="FQ9" s="21" t="n"/>
-      <c r="FR9" s="21" t="n"/>
-      <c r="FS9" s="21" t="n"/>
-      <c r="FT9" s="21" t="n"/>
-      <c r="FU9" s="21" t="n"/>
-      <c r="FV9" s="21" t="n"/>
-      <c r="FW9" s="21" t="n"/>
-      <c r="FX9" s="21" t="n"/>
-      <c r="FY9" s="21" t="n"/>
-      <c r="FZ9" s="21" t="n"/>
-      <c r="GA9" s="21" t="n"/>
-      <c r="GB9" s="21" t="n"/>
-      <c r="GC9" s="21" t="n"/>
-      <c r="GD9" s="21" t="n"/>
-      <c r="GE9" s="21" t="n"/>
-      <c r="GF9" s="21" t="n"/>
-      <c r="GG9" s="21" t="n"/>
-      <c r="GH9" s="21" t="n"/>
-      <c r="GI9" s="21" t="n"/>
-      <c r="GJ9" s="21" t="n"/>
-      <c r="GK9" s="21" t="n"/>
-      <c r="GL9" s="21" t="n"/>
-      <c r="GM9" s="21" t="n"/>
-      <c r="GN9" s="21" t="n"/>
-      <c r="GO9" s="21" t="n"/>
-      <c r="GP9" s="21" t="n"/>
-      <c r="GQ9" s="21" t="n"/>
-      <c r="GR9" s="21" t="n"/>
-      <c r="GS9" s="21" t="n"/>
-      <c r="GT9" s="21" t="n"/>
-      <c r="GU9" s="21" t="n"/>
-      <c r="GV9" s="21" t="n"/>
-      <c r="GW9" s="21" t="n"/>
-      <c r="GX9" s="21" t="n"/>
-      <c r="GY9" s="21" t="n"/>
-      <c r="GZ9" s="21" t="n"/>
-      <c r="HA9" s="21" t="n"/>
-      <c r="HB9" s="21" t="n"/>
-      <c r="HC9" s="21" t="n"/>
-      <c r="HD9" s="21" t="n"/>
-      <c r="HE9" s="21" t="n"/>
-      <c r="HF9" s="21" t="n"/>
-      <c r="HG9" s="21" t="n"/>
-      <c r="HH9" s="21" t="n"/>
-      <c r="HI9" s="21" t="n"/>
+      <c r="J9" s="61" t="n"/>
+      <c r="K9" s="39" t="n"/>
+      <c r="L9" s="39" t="n"/>
+      <c r="M9" s="39" t="n"/>
+      <c r="N9" s="39" t="n"/>
+      <c r="O9" s="39" t="n"/>
+      <c r="P9" s="39" t="n"/>
+      <c r="Q9" s="39" t="n"/>
+      <c r="R9" s="39" t="n"/>
+      <c r="S9" s="39" t="n"/>
+      <c r="T9" s="39" t="n"/>
+      <c r="U9" s="39" t="n"/>
+      <c r="V9" s="39" t="n"/>
+      <c r="W9" s="39" t="n"/>
+      <c r="X9" s="39" t="n"/>
+      <c r="Y9" s="39" t="n"/>
+      <c r="Z9" s="39" t="n"/>
+      <c r="AA9" s="39" t="n"/>
+      <c r="AB9" s="39" t="n"/>
+      <c r="AC9" s="39" t="n"/>
+      <c r="AD9" s="39" t="n"/>
+      <c r="AE9" s="39" t="n"/>
+      <c r="AF9" s="39" t="n"/>
+      <c r="AG9" s="39" t="n"/>
+      <c r="AH9" s="39" t="n"/>
+      <c r="AI9" s="39" t="n"/>
+      <c r="AJ9" s="39" t="n"/>
+      <c r="AK9" s="39" t="n"/>
+      <c r="AL9" s="39" t="n"/>
+      <c r="AM9" s="39" t="n"/>
+      <c r="AN9" s="39" t="n"/>
+      <c r="AO9" s="39" t="n"/>
+      <c r="AP9" s="39" t="n"/>
+      <c r="AQ9" s="39" t="n"/>
+      <c r="AR9" s="39" t="n"/>
+      <c r="AS9" s="39" t="n"/>
+      <c r="AT9" s="39" t="n"/>
+      <c r="AU9" s="39" t="n"/>
+      <c r="AV9" s="39" t="n"/>
+      <c r="AW9" s="39" t="n"/>
+      <c r="AX9" s="39" t="n"/>
+      <c r="AY9" s="39" t="n"/>
+      <c r="AZ9" s="39" t="n"/>
+      <c r="BA9" s="39" t="n"/>
+      <c r="BB9" s="39" t="n"/>
+      <c r="BC9" s="39" t="n"/>
+      <c r="BD9" s="39" t="n"/>
+      <c r="BE9" s="39" t="n"/>
+      <c r="BF9" s="39" t="n"/>
+      <c r="BG9" s="39" t="n"/>
+      <c r="BH9" s="39" t="n"/>
+      <c r="BI9" s="39" t="n"/>
+      <c r="BJ9" s="39" t="n"/>
+      <c r="BK9" s="39" t="n"/>
+      <c r="BL9" s="39" t="n"/>
+      <c r="BM9" s="39" t="n"/>
+      <c r="BN9" s="39" t="n"/>
+      <c r="BO9" s="39" t="n"/>
+      <c r="BP9" s="39" t="n"/>
+      <c r="BQ9" s="39" t="n"/>
+      <c r="BR9" s="39" t="n"/>
+      <c r="BS9" s="39" t="n"/>
+      <c r="BT9" s="39" t="n"/>
+      <c r="BU9" s="39" t="n"/>
+      <c r="BV9" s="39" t="n"/>
+      <c r="BW9" s="39" t="n"/>
+      <c r="BX9" s="39" t="n"/>
+      <c r="BY9" s="39" t="n"/>
+      <c r="BZ9" s="39" t="n"/>
+      <c r="CA9" s="39" t="n"/>
+      <c r="CB9" s="39" t="n"/>
+      <c r="CC9" s="39" t="n"/>
+      <c r="CD9" s="39" t="n"/>
+      <c r="CE9" s="39" t="n"/>
+      <c r="CF9" s="39" t="n"/>
+      <c r="CG9" s="39" t="n"/>
+      <c r="CH9" s="39" t="n"/>
+      <c r="CI9" s="39" t="n"/>
+      <c r="CJ9" s="39" t="n"/>
+      <c r="CK9" s="39" t="n"/>
+      <c r="CL9" s="39" t="n"/>
+      <c r="CM9" s="39" t="n"/>
+      <c r="CN9" s="39" t="n"/>
+      <c r="CO9" s="39" t="n"/>
+      <c r="CP9" s="39" t="n"/>
+      <c r="CQ9" s="39" t="n"/>
+      <c r="CR9" s="39" t="n"/>
+      <c r="CS9" s="39" t="n"/>
+      <c r="CT9" s="39" t="n"/>
+      <c r="CU9" s="39" t="n"/>
+      <c r="CV9" s="39" t="n"/>
+      <c r="CW9" s="39" t="n"/>
+      <c r="CX9" s="39" t="n"/>
+      <c r="CY9" s="39" t="n"/>
+      <c r="CZ9" s="39" t="n"/>
+      <c r="DA9" s="39" t="n"/>
+      <c r="DB9" s="39" t="n"/>
+      <c r="DC9" s="39" t="n"/>
+      <c r="DD9" s="39" t="n"/>
+      <c r="DE9" s="39" t="n"/>
+      <c r="DF9" s="39" t="n"/>
+      <c r="DG9" s="39" t="n"/>
+      <c r="DH9" s="39" t="n"/>
+      <c r="DI9" s="39" t="n"/>
+      <c r="DJ9" s="39" t="n"/>
+      <c r="DK9" s="39" t="n"/>
+      <c r="DL9" s="39" t="n"/>
+      <c r="DM9" s="39" t="n"/>
+      <c r="DN9" s="39" t="n"/>
+      <c r="DO9" s="39" t="n"/>
+      <c r="DP9" s="39" t="n"/>
+      <c r="DQ9" s="39" t="n"/>
+      <c r="DR9" s="39" t="n"/>
+      <c r="DS9" s="39" t="n"/>
+      <c r="DT9" s="39" t="n"/>
+      <c r="DU9" s="39" t="n"/>
+      <c r="DV9" s="39" t="n"/>
+      <c r="DW9" s="39" t="n"/>
+      <c r="DX9" s="39" t="n"/>
+      <c r="DY9" s="39" t="n"/>
+      <c r="DZ9" s="39" t="n"/>
+      <c r="EA9" s="39" t="n"/>
+      <c r="EB9" s="39" t="n"/>
+      <c r="EC9" s="39" t="n"/>
+      <c r="ED9" s="39" t="n"/>
+      <c r="EE9" s="39" t="n"/>
+      <c r="EF9" s="39" t="n"/>
+      <c r="EG9" s="39" t="n"/>
+      <c r="EH9" s="39" t="n"/>
+      <c r="EI9" s="39" t="n"/>
+      <c r="EJ9" s="39" t="n"/>
+      <c r="EK9" s="39" t="n"/>
+      <c r="EL9" s="39" t="n"/>
+      <c r="EM9" s="39" t="n"/>
+      <c r="EN9" s="39" t="n"/>
+      <c r="EO9" s="39" t="n"/>
+      <c r="EP9" s="39" t="n"/>
+      <c r="EQ9" s="39" t="n"/>
+      <c r="ER9" s="39" t="n"/>
+      <c r="ES9" s="39" t="n"/>
+      <c r="ET9" s="39" t="n"/>
+      <c r="EU9" s="39" t="n"/>
+      <c r="EV9" s="39" t="n"/>
+      <c r="EW9" s="39" t="n"/>
+      <c r="EX9" s="39" t="n"/>
+      <c r="EY9" s="39" t="n"/>
+      <c r="EZ9" s="39" t="n"/>
+      <c r="FA9" s="39" t="n"/>
+      <c r="FB9" s="39" t="n"/>
+      <c r="FC9" s="39" t="n"/>
+      <c r="FD9" s="39" t="n"/>
+      <c r="FE9" s="39" t="n"/>
+      <c r="FF9" s="39" t="n"/>
+      <c r="FG9" s="39" t="n"/>
+      <c r="FH9" s="39" t="n"/>
+      <c r="FI9" s="39" t="n"/>
+      <c r="FJ9" s="39" t="n"/>
+      <c r="FK9" s="39" t="n"/>
+      <c r="FL9" s="39" t="n"/>
+      <c r="FM9" s="39" t="n"/>
+      <c r="FN9" s="39" t="n"/>
+      <c r="FO9" s="39" t="n"/>
+      <c r="FP9" s="39" t="n"/>
+      <c r="FQ9" s="39" t="n"/>
+      <c r="FR9" s="39" t="n"/>
+      <c r="FS9" s="39" t="n"/>
+      <c r="FT9" s="39" t="n"/>
+      <c r="FU9" s="39" t="n"/>
+      <c r="FV9" s="39" t="n"/>
+      <c r="FW9" s="39" t="n"/>
+      <c r="FX9" s="39" t="n"/>
+      <c r="FY9" s="39" t="n"/>
+      <c r="FZ9" s="39" t="n"/>
+      <c r="GA9" s="39" t="n"/>
+      <c r="GB9" s="39" t="n"/>
+      <c r="GC9" s="39" t="n"/>
+      <c r="GD9" s="39" t="n"/>
+      <c r="GE9" s="39" t="n"/>
+      <c r="GF9" s="39" t="n"/>
+      <c r="GG9" s="39" t="n"/>
+      <c r="GH9" s="39" t="n"/>
+      <c r="GI9" s="39" t="n"/>
+      <c r="GJ9" s="39" t="n"/>
+      <c r="GK9" s="39" t="n"/>
+      <c r="GL9" s="39" t="n"/>
+      <c r="GM9" s="39" t="n"/>
+      <c r="GN9" s="39" t="n"/>
+      <c r="GO9" s="39" t="n"/>
+      <c r="GP9" s="39" t="n"/>
+      <c r="GQ9" s="39" t="n"/>
+      <c r="GR9" s="39" t="n"/>
+      <c r="GS9" s="39" t="n"/>
+      <c r="GT9" s="39" t="n"/>
+      <c r="GU9" s="39" t="n"/>
+      <c r="GV9" s="39" t="n"/>
+      <c r="GW9" s="39" t="n"/>
+      <c r="GX9" s="39" t="n"/>
+      <c r="GY9" s="39" t="n"/>
+      <c r="GZ9" s="39" t="n"/>
+      <c r="HA9" s="39" t="n"/>
+      <c r="HB9" s="39" t="n"/>
+      <c r="HC9" s="39" t="n"/>
+      <c r="HD9" s="39" t="n"/>
+      <c r="HE9" s="39" t="n"/>
+      <c r="HF9" s="39" t="n"/>
+      <c r="HG9" s="39" t="n"/>
+      <c r="HH9" s="39" t="n"/>
+      <c r="HI9" s="39" t="n"/>
     </row>
     <row r="10" ht="44.1" customHeight="1" s="2">
       <c r="A10" s="16" t="n">
